--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,15 +454,20 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>技能图标</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>技能效果ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>基础冷却</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>失控概率加成</t>
         </is>
@@ -506,15 +511,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>UI 图标资源 Id；缺/空=无图</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>FK → SkillEffectConfig.SkillEffectId</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>≥0 秒；实际 CD 见 §3.12 公式</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>可正可负；缺省 0；按等级查行后求和</t>
         </is>
@@ -558,15 +568,20 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>IconAssetId</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>SkillEffectId</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BaseCooldownSeconds</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>LossOfControlChanceBonus</t>
         </is>
@@ -593,7 +608,6 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>技能01</t>
@@ -604,17 +618,17 @@
           <t>技能01展示描述</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -623,13 +637,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skill_02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Skill_01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -641,37 +653,35 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>技能02</t>
+          <t>技能01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>技能02展示描述</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SkillEffect_02</t>
-        </is>
-      </c>
+          <t>技能01展示描述</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>SkillEffect_01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skill_03</t>
+          <t>Skill_02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -681,7 +691,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mode2</t>
+          <t>Mode1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -689,37 +699,36 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>技能03</t>
+          <t>技能02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>技能03展示描述</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SkillEffect_03</t>
+          <t>技能02展示描述</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>SkillEffect_02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Skill_04</t>
+          <t>Skill_03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -729,7 +738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mode1</t>
+          <t>Mode2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,37 +746,36 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>技能04</t>
+          <t>技能03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>技能04展示描述</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SkillEffect_04</t>
+          <t>技能03展示描述</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>SkillEffect_03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Skill_05</t>
+          <t>Skill_04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -782,40 +790,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EnemySingle</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>技能05</t>
+          <t>技能04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>技能05展示描述</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SkillEffect_05</t>
+          <t>技能04展示描述</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>SkillEffect_04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skill_06</t>
+          <t>Skill_05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -825,45 +832,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mode2</t>
+          <t>Mode1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>EnemySingle</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>技能06</t>
+          <t>技能05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>技能06展示描述</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>SkillEffect_06</t>
+          <t>技能05展示描述</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>SkillEffect_05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Skill_07</t>
+          <t>Skill_06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -873,45 +879,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mode1</t>
+          <t>Mode2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CurrentNormalAttackTarget</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Self</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>技能07</t>
+          <t>技能06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>技能07展示描述</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SkillEffect_07</t>
+          <t>技能06展示描述</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>SkillEffect_06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-0.01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skill_08</t>
+          <t>Skill_07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -926,40 +931,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AllySingle</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>技能08</t>
+          <t>技能07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>技能08展示描述</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SkillEffect_08</t>
+          <t>技能07展示描述</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>SkillEffect_07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skill_09</t>
+          <t>Skill_08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,84 +973,129 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mode2</t>
+          <t>Mode1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GroundPoint</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>AllySingle</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>技能09</t>
+          <t>技能08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>技能09展示描述</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>SkillEffect_09</t>
+          <t>技能08展示描述</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>SkillEffect_08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Skill_09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GroundPoint</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>技能09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>技能09展示描述</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SkillEffect_09</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>EnemyAll</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>技能10</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>技能10展示描述</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>SkillEffect_10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="180">
   <si>
     <t>技能ID</t>
   </si>
@@ -136,166 +136,442 @@
     <t>Mode2</t>
   </si>
   <si>
-    <t>CurrentNormalAttackTarget</t>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>敌人普攻命中Self</t>
   </si>
   <si>
     <t>格挡</t>
   </si>
   <si>
-    <t>敌人的普通攻击有10%的概率伤害变为0（但还是判断为命中）</t>
-  </si>
-  <si>
-    <t>SkillEffect_01</t>
+    <t>敌人本次普通攻击有10%的概率伤害变为0（但还是判断为命中）</t>
+  </si>
+  <si>
+    <t>SkillEffect_01_1</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
+    <t>敌人本次普通攻击有15%的概率伤害变为0（但还是判断为命中）</t>
+  </si>
+  <si>
+    <t>SkillEffect_01_2</t>
+  </si>
+  <si>
+    <t>敌人本次普通攻击有20%的概率伤害变为0（但还是判断为命中）</t>
+  </si>
+  <si>
+    <t>SkillEffect_01_3</t>
+  </si>
+  <si>
+    <t>敌人本次普通攻击有25%的概率伤害变为0（但还是判断为命中）</t>
+  </si>
+  <si>
+    <t>SkillEffect_01_4</t>
+  </si>
+  <si>
+    <t>敌人本次普通攻击有30%的概率伤害变为0（但还是判断为命中）</t>
+  </si>
+  <si>
+    <t>SkillEffect_01_5</t>
+  </si>
+  <si>
     <t>Skill_02</t>
   </si>
   <si>
+    <t>自身血量=100%</t>
+  </si>
+  <si>
     <t>舒适</t>
   </si>
   <si>
-    <t>未受伤的情况下，伤害提升5%</t>
-  </si>
-  <si>
-    <t>SkillEffect_02</t>
+    <t>伤害提升5%</t>
+  </si>
+  <si>
+    <t>SkillEffect_02_1</t>
+  </si>
+  <si>
+    <t>伤害提升10%</t>
+  </si>
+  <si>
+    <t>SkillEffect_02_2</t>
+  </si>
+  <si>
+    <t>伤害提升15%</t>
+  </si>
+  <si>
+    <t>SkillEffect_02_3</t>
+  </si>
+  <si>
+    <t>伤害提升20%</t>
+  </si>
+  <si>
+    <t>SkillEffect_02_4</t>
+  </si>
+  <si>
+    <t>伤害提升25%</t>
+  </si>
+  <si>
+    <t>SkillEffect_02_5</t>
   </si>
   <si>
     <t>Skill_03</t>
   </si>
   <si>
+    <t>EnemySingle</t>
+  </si>
+  <si>
     <t>连发</t>
   </si>
   <si>
-    <t>攻击目标时连续攻击3次，CD 10秒</t>
-  </si>
-  <si>
-    <t>SkillEffect_03</t>
+    <t>攻击目标时连续攻击3次</t>
+  </si>
+  <si>
+    <t>SkillEffect_03_1</t>
+  </si>
+  <si>
+    <t>SkillEffect_03_2</t>
+  </si>
+  <si>
+    <t>SkillEffect_03_3</t>
+  </si>
+  <si>
+    <t>SkillEffect_03_4</t>
+  </si>
+  <si>
+    <t>SkillEffect_03_5</t>
   </si>
   <si>
     <t>Skill_04</t>
   </si>
   <si>
+    <t>普攻攻击新目标敌人的第一次</t>
+  </si>
+  <si>
     <t>先发制人</t>
   </si>
   <si>
-    <t>攻击1名敌人的第一次攻击伤害提升20%</t>
-  </si>
-  <si>
-    <t>SkillEffect_04</t>
+    <t>攻击伤害提升20%</t>
+  </si>
+  <si>
+    <t>SkillEffect_04_1</t>
+  </si>
+  <si>
+    <t>攻击伤害提升30%</t>
+  </si>
+  <si>
+    <t>SkillEffect_04_2</t>
+  </si>
+  <si>
+    <t>攻击伤害提升40%</t>
+  </si>
+  <si>
+    <t>SkillEffect_04_3</t>
+  </si>
+  <si>
+    <t>攻击伤害提升50%</t>
+  </si>
+  <si>
+    <t>SkillEffect_04_4</t>
+  </si>
+  <si>
+    <t>攻击伤害提升60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_04_5</t>
   </si>
   <si>
     <t>Skill_05</t>
   </si>
   <si>
+    <t>敌人的本次攻击导致Self死亡</t>
+  </si>
+  <si>
     <t>坚挺</t>
   </si>
   <si>
-    <t>当这一次受伤将导致死亡时，生命值强制变为1点血，并无敌1秒钟</t>
-  </si>
-  <si>
-    <t>SkillEffect_05</t>
+    <t>士兵自身生命值强制变为1点血，并无敌1秒钟</t>
+  </si>
+  <si>
+    <t>SkillEffect_05_1</t>
+  </si>
+  <si>
+    <t>士兵自身生命值强制变为1点血，并无敌2秒钟</t>
+  </si>
+  <si>
+    <t>SkillEffect_05_2</t>
+  </si>
+  <si>
+    <t>士兵自身生命值强制变为1点血，并无敌3秒钟</t>
+  </si>
+  <si>
+    <t>SkillEffect_05_3</t>
+  </si>
+  <si>
+    <t>士兵自身生命值强制变为1点血，并无敌4秒钟</t>
+  </si>
+  <si>
+    <t>SkillEffect_05_4</t>
+  </si>
+  <si>
+    <t>士兵自身生命值强制变为1点血，并无敌5秒钟</t>
+  </si>
+  <si>
+    <t>SkillEffect_05_5</t>
   </si>
   <si>
     <t>Skill_06</t>
   </si>
   <si>
-    <t>EnemySingle</t>
-  </si>
-  <si>
-    <t>击飞</t>
-  </si>
-  <si>
-    <t>命中敌人后，有10%的概率对目标敌人四周的士兵产生击飞</t>
-  </si>
-  <si>
-    <t>SkillEffect_06</t>
+    <t>GroundPoint</t>
+  </si>
+  <si>
+    <t>士兵普攻命中敌人</t>
+  </si>
+  <si>
+    <t>震晕</t>
+  </si>
+  <si>
+    <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”1秒（“击晕”生效的时间内，无法攻击和移动）</t>
+  </si>
+  <si>
+    <t>SkillEffect_06_1</t>
+  </si>
+  <si>
+    <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”2秒（“击晕”生效的时间内，无法攻击和移动）</t>
+  </si>
+  <si>
+    <t>SkillEffect_06_2</t>
+  </si>
+  <si>
+    <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”3秒（“击晕”生效的时间内，无法攻击和移动）</t>
+  </si>
+  <si>
+    <t>SkillEffect_06_3</t>
+  </si>
+  <si>
+    <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”4秒（“击晕”生效的时间内，无法攻击和移动）</t>
+  </si>
+  <si>
+    <t>SkillEffect_06_4</t>
+  </si>
+  <si>
+    <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”5秒（“击晕”生效的时间内，无法攻击和移动）</t>
+  </si>
+  <si>
+    <t>SkillEffect_06_5</t>
   </si>
   <si>
     <t>Skill_07</t>
   </si>
   <si>
-    <t>Self</t>
-  </si>
-  <si>
     <t>冰冻</t>
   </si>
   <si>
-    <t>范围减少攻速和移动速度</t>
-  </si>
-  <si>
-    <t>SkillEffect_07</t>
+    <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续2秒</t>
+  </si>
+  <si>
+    <t>SkillEffect_07_1</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续3秒</t>
+  </si>
+  <si>
+    <t>SkillEffect_07_2</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续4秒</t>
+  </si>
+  <si>
+    <t>SkillEffect_07_3</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续5秒</t>
+  </si>
+  <si>
+    <t>SkillEffect_07_4</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续6秒</t>
+  </si>
+  <si>
+    <t>SkillEffect_07_5</t>
   </si>
   <si>
     <t>Skill_08</t>
   </si>
   <si>
+    <t>目标敌人的MonsterType是精英(Elite)</t>
+  </si>
+  <si>
     <t>精英克制</t>
   </si>
   <si>
-    <t>如果攻击的目标是“精英”怪物则攻击的伤害增加50%</t>
-  </si>
-  <si>
-    <t>SkillEffect_08</t>
+    <t>攻击的伤害增加50%</t>
+  </si>
+  <si>
+    <t>SkillEffect_08_1</t>
+  </si>
+  <si>
+    <t>攻击的伤害增加60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_08_2</t>
+  </si>
+  <si>
+    <t>攻击的伤害增加70%</t>
+  </si>
+  <si>
+    <t>SkillEffect_08_3</t>
+  </si>
+  <si>
+    <t>攻击的伤害增加80%</t>
+  </si>
+  <si>
+    <t>SkillEffect_08_4</t>
+  </si>
+  <si>
+    <t>攻击的伤害增加90%</t>
+  </si>
+  <si>
+    <t>SkillEffect_08_5</t>
   </si>
   <si>
     <t>Skill_09</t>
   </si>
   <si>
-    <t>AllySingle</t>
-  </si>
-  <si>
     <t>渐入佳境</t>
   </si>
   <si>
-    <t>每存活10秒，攻击增加3%，最大60%</t>
-  </si>
-  <si>
-    <t>SkillEffect_09</t>
+    <t>攻击增加3%，可以叠加效果，最大叠加到60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_09_1</t>
+  </si>
+  <si>
+    <t>攻击增加5%，可以叠加效果，最大叠加到60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_09_2</t>
+  </si>
+  <si>
+    <t>攻击增加7%，可以叠加效果，最大叠加到60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_09_3</t>
+  </si>
+  <si>
+    <t>攻击增加9%，可以叠加效果，最大叠加到60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_09_4</t>
+  </si>
+  <si>
+    <t>攻击增加12%，可以叠加效果，最大叠加到60%</t>
+  </si>
+  <si>
+    <t>SkillEffect_09_5</t>
   </si>
   <si>
     <t>Skill_10</t>
   </si>
   <si>
-    <t>GroundPoint</t>
-  </si>
-  <si>
     <t>贯穿</t>
   </si>
   <si>
-    <t>发射的箭矢命中1名敌人后可以穿过此敌人继续向后飞</t>
-  </si>
-  <si>
-    <t>SkillEffect_10</t>
+    <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下1名敌人，造成100%的伤害</t>
+  </si>
+  <si>
+    <t>SkillEffect_10_1</t>
+  </si>
+  <si>
+    <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下2名敌人，造成100%的伤害</t>
+  </si>
+  <si>
+    <t>SkillEffect_10_2</t>
+  </si>
+  <si>
+    <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下3名敌人，造成100%的伤害</t>
+  </si>
+  <si>
+    <t>SkillEffect_10_3</t>
+  </si>
+  <si>
+    <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下4名敌人，造成100%的伤害</t>
+  </si>
+  <si>
+    <t>SkillEffect_10_4</t>
+  </si>
+  <si>
+    <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下5名敌人，造成100%的伤害</t>
+  </si>
+  <si>
+    <t>SkillEffect_10_5</t>
   </si>
   <si>
     <t>Skill_11</t>
   </si>
   <si>
-    <t>EnemyAll</t>
-  </si>
-  <si>
     <t>灼烧</t>
   </si>
   <si>
-    <t>范围持续伤害</t>
-  </si>
-  <si>
-    <t>SkillEffect_11</t>
+    <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续2秒，再次施加“灼烧”则叠加灼烧的时间）</t>
+  </si>
+  <si>
+    <t>SkillEffect_11_1</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续3秒，再次施加“灼烧”则叠加灼烧的时间）</t>
+  </si>
+  <si>
+    <t>SkillEffect_11_2</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续4秒，再次施加“灼烧”则叠加灼烧的时间）</t>
+  </si>
+  <si>
+    <t>SkillEffect_11_3</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续5秒，再次施加“灼烧”则叠加灼烧的时间）</t>
+  </si>
+  <si>
+    <t>SkillEffect_11_4</t>
+  </si>
+  <si>
+    <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续6秒，再次施加“灼烧”则叠加灼烧的时间）</t>
+  </si>
+  <si>
+    <t>SkillEffect_11_5</t>
   </si>
   <si>
     <t>Skill_12</t>
   </si>
   <si>
+    <t>当开始寻找新的攻击目标</t>
+  </si>
+  <si>
     <t>瞬移</t>
   </si>
   <si>
-    <t>当开始寻找新的攻击目标时，会寻找距离最远的敌人并瞬移到该敌人的背后</t>
-  </si>
-  <si>
-    <t>SkillEffect_12</t>
+    <t>更换选择的目标为“距离自己最远的敌人”，目标确定后“瞬移”到该敌人的背后</t>
+  </si>
+  <si>
+    <t>SkillEffect_12_1</t>
+  </si>
+  <si>
+    <t>SkillEffect_12_2</t>
+  </si>
+  <si>
+    <t>SkillEffect_12_3</t>
+  </si>
+  <si>
+    <t>SkillEffect_12_4</t>
+  </si>
+  <si>
+    <t>SkillEffect_12_5</t>
   </si>
 </sst>
 </file>
@@ -308,24 +584,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -790,19 +1052,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -811,146 +1082,139 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1299,11 +1563,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="4" width="23.875" customWidth="1"/>
-    <col min="7" max="7" width="33.5" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="78" customWidth="1"/>
     <col min="9" max="9" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1425,31 +1690,34 @@
       <c r="D4" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
       <c r="F4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>33</v>
@@ -1457,31 +1725,34 @@
       <c r="D5" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
       <c r="F5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" t="s">
-        <v>42</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>33</v>
@@ -1489,31 +1760,34 @@
       <c r="D6" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
       <c r="F6" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
         <v>43</v>
       </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>33</v>
@@ -1521,31 +1795,34 @@
       <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
       <c r="F7" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>33</v>
@@ -1553,28 +1830,31 @@
       <c r="D8" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
       <c r="F8" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -1583,65 +1863,71 @@
         <v>33</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>61</v>
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>33</v>
@@ -1649,92 +1935,101 @@
       <c r="D11" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
       <c r="F11" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>70</v>
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>75</v>
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
@@ -1743,61 +2038,1669 @@
         <v>33</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>82</v>
+        <v>63</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15">
+        <v>40</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16">
+        <v>30</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="2">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="2">
+      <c r="F24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" t="s">
+        <v>87</v>
+      </c>
+      <c r="J24">
+        <v>60</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" t="s">
+        <v>89</v>
+      </c>
+      <c r="J25">
+        <v>60</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J26">
+        <v>60</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="2">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" t="s">
+        <v>93</v>
+      </c>
+      <c r="J27">
+        <v>60</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="2">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28">
+        <v>60</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="2">
         <v>1</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15">
+      <c r="C29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" t="s">
+        <v>101</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I30" t="s">
+        <v>103</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="2">
+        <v>3</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" t="s">
+        <v>105</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="2">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I33" t="s">
+        <v>109</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="2">
         <v>1</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="K16" s="7"/>
+      <c r="C34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I34" t="s">
+        <v>113</v>
+      </c>
+      <c r="J34">
+        <v>10</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="2">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I35" t="s">
+        <v>115</v>
+      </c>
+      <c r="J35">
+        <v>10</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="2">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I36" t="s">
+        <v>117</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="2">
+        <v>4</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" t="s">
+        <v>119</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="2">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I38" t="s">
+        <v>121</v>
+      </c>
+      <c r="J38">
+        <v>10</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I39" t="s">
+        <v>126</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="2">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I40" t="s">
+        <v>128</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="2">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I42" t="s">
+        <v>132</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" t="s">
+        <v>123</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" t="s">
+        <v>134</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I44" t="s">
+        <v>138</v>
+      </c>
+      <c r="J44">
+        <v>10</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I45" t="s">
+        <v>140</v>
+      </c>
+      <c r="J45">
+        <v>10</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="2">
+        <v>3</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I46" t="s">
+        <v>142</v>
+      </c>
+      <c r="J46">
+        <v>10</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I47" t="s">
+        <v>144</v>
+      </c>
+      <c r="J47">
+        <v>10</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="2">
+        <v>5</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I48" t="s">
+        <v>146</v>
+      </c>
+      <c r="J48">
+        <v>10</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" s="2">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I49" t="s">
+        <v>150</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" s="2">
+        <v>2</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I50" t="s">
+        <v>152</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I51" t="s">
+        <v>154</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>147</v>
+      </c>
+      <c r="B52" s="2">
+        <v>4</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I52" t="s">
+        <v>156</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I53" t="s">
+        <v>158</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="2">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I54" t="s">
+        <v>162</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="2">
+        <v>2</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I55" t="s">
+        <v>164</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" s="2">
+        <v>3</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" t="s">
+        <v>166</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>159</v>
+      </c>
+      <c r="B57" s="2">
+        <v>4</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I57" t="s">
+        <v>168</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>159</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I58" t="s">
+        <v>170</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I59" t="s">
+        <v>175</v>
+      </c>
+      <c r="J59">
+        <v>60</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="2">
+        <v>2</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" t="s">
+        <v>172</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I60" t="s">
+        <v>176</v>
+      </c>
+      <c r="J60">
+        <v>50</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="2">
+        <v>3</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E61" t="s">
+        <v>172</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I61" t="s">
+        <v>177</v>
+      </c>
+      <c r="J61">
+        <v>40</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" s="2">
+        <v>4</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I62" t="s">
+        <v>178</v>
+      </c>
+      <c r="J62">
+        <v>30</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="2">
+        <v>5</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E63" t="s">
+        <v>172</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I63" t="s">
+        <v>179</v>
+      </c>
+      <c r="J63">
+        <v>20</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.75" customWidth="1" min="4" max="4"/>
@@ -1079,50 +1079,55 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>阵型ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>技能CD模式</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>技能释放目标</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>额外激活条件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>技能名称</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>技能展示描述</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>技能图标</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>技能效果ID</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>基础冷却</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>失控概率加成</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>效果已实现</t>
         </is>
@@ -1141,50 +1146,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>可选；空=普通士兵技能；非空=阵型标记技能 FK→TacticalFormationConfig</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Mode1=开战起算CD；Mode2=开战CD=0，释放后再进CD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Self|AllySingle|AllyAll|EnemySingle|EnemyAll|GroundPoint|CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>默认空；编码后续专题</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>展示文字或本地化 Key</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>展示文字或本地化 Key</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>UI 图标资源 Id；缺/空=无图</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>FK → SkillEffectConfig.SkillEffectId</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>≥0 秒；实际 CD 见 §3.12 公式</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>可正可负；缺省 0；按等级查行后求和</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Demo 战斗效果是否已接线；不驱动战斗；UI-021 绿/红</t>
         </is>
@@ -1201,52 +1211,57 @@
           <t>SkillLevel</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FormationId</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>CooldownMode</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>CastTarget</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>ExtraActivationCondition</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>IconAssetId</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>SkillEffectId</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>BaseCooldownSeconds</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>LossOfControlChanceBonus</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>EffectImplemented</t>
         </is>
@@ -1261,50 +1276,50 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>敌人普攻命中Self</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>敌人本次普通攻击有10%的概率伤害变为0（但还是判断为命中）</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SkillEffect_01_1</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1317,50 +1332,50 @@
       <c r="B5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>敌人普攻命中Self</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>敌人本次普通攻击有15%的概率伤害变为0（但还是判断为命中）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SkillEffect_01_2</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1373,50 +1388,50 @@
       <c r="B6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>敌人普攻命中Self</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>敌人本次普通攻击有20%的概率伤害变为0（但还是判断为命中）</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SkillEffect_01_3</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1429,50 +1444,50 @@
       <c r="B7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>敌人普攻命中Self</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>敌人本次普通攻击有25%的概率伤害变为0（但还是判断为命中）</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SkillEffect_01_4</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1485,50 +1500,50 @@
       <c r="B8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>敌人普攻命中Self</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>敌人本次普通攻击有30%的概率伤害变为0（但还是判断为命中）</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SkillEffect_01_5</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1541,50 +1556,50 @@
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>自身血量=100%</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>舒适</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>伤害提升5%</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Skill_02</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SkillEffect_02_1</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1597,50 +1612,50 @@
       <c r="B10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>自身血量=100%</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>舒适</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>伤害提升10%</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Skill_02</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SkillEffect_02_2</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1653,50 +1668,50 @@
       <c r="B11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>自身血量=100%</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>舒适</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>伤害提升15%</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Skill_02</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SkillEffect_02_3</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1709,50 +1724,50 @@
       <c r="B12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>自身血量=100%</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>舒适</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>伤害提升20%</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Skill_02</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SkillEffect_02_4</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1765,50 +1780,50 @@
       <c r="B13" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>自身血量=100%</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>舒适</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>伤害提升25%</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Skill_02</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SkillEffect_02_5</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1821,45 +1836,45 @@
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>连发</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>攻击目标时连续攻击3次</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Skill_03</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SkillEffect_03_1</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>50</v>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1872,45 +1887,45 @@
       <c r="B15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>连发</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>攻击目标时连续攻击3次</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Skill_03</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>SkillEffect_03_2</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>40</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1923,45 +1938,45 @@
       <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>连发</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>攻击目标时连续攻击3次</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Skill_03</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>SkillEffect_03_3</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>30</v>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1974,45 +1989,45 @@
       <c r="B17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>连发</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>攻击目标时连续攻击3次</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Skill_03</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>SkillEffect_03_4</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>20</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2025,45 +2040,45 @@
       <c r="B18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>连发</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>攻击目标时连续攻击3次</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Skill_03</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>SkillEffect_03_5</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2076,50 +2091,50 @@
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>普攻攻击新目标敌人的第一次</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>先发制人</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>攻击伤害提升20%</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Skill_04</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>SkillEffect_04_1</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2132,50 +2147,50 @@
       <c r="B20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>普攻攻击新目标敌人的第一次</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>先发制人</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>攻击伤害提升30%</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Skill_04</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>SkillEffect_04_2</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2188,50 +2203,50 @@
       <c r="B21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>普攻攻击新目标敌人的第一次</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>先发制人</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>攻击伤害提升40%</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Skill_04</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>SkillEffect_04_3</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2244,50 +2259,50 @@
       <c r="B22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>普攻攻击新目标敌人的第一次</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>先发制人</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>攻击伤害提升50%</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Skill_04</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>SkillEffect_04_4</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2300,50 +2315,50 @@
       <c r="B23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>普攻攻击新目标敌人的第一次</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>先发制人</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>攻击伤害提升60%</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Skill_04</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>SkillEffect_04_5</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2356,50 +2371,50 @@
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>敌人的本次攻击导致Self死亡</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>坚挺</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>士兵自身生命值强制变为1点血，并无敌1秒钟</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Skill_05</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>SkillEffect_05_1</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>60</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2412,50 +2427,50 @@
       <c r="B25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>敌人的本次攻击导致Self死亡</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>坚挺</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>士兵自身生命值强制变为1点血，并无敌2秒钟</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Skill_05</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>SkillEffect_05_2</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>60</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2468,50 +2483,50 @@
       <c r="B26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>敌人的本次攻击导致Self死亡</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>坚挺</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>士兵自身生命值强制变为1点血，并无敌3秒钟</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Skill_05</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>SkillEffect_05_3</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>60</v>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2524,50 +2539,50 @@
       <c r="B27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>敌人的本次攻击导致Self死亡</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>坚挺</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>士兵自身生命值强制变为1点血，并无敌4秒钟</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Skill_05</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>SkillEffect_05_4</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>60</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2580,50 +2595,50 @@
       <c r="B28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>敌人的本次攻击导致Self死亡</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>坚挺</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>士兵自身生命值强制变为1点血，并无敌5秒钟</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Skill_05</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>SkillEffect_05_5</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>60</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2636,50 +2651,50 @@
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>士兵普攻命中敌人</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>震晕</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”1秒（“击晕”生效的时间内，无法攻击和移动）</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Skill_06</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>SkillEffect_06_1</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2692,50 +2707,50 @@
       <c r="B30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>士兵普攻命中敌人</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>震晕</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”2秒（“击晕”生效的时间内，无法攻击和移动）</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Skill_06</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>SkillEffect_06_2</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2748,50 +2763,50 @@
       <c r="B31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>士兵普攻命中敌人</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>震晕</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”3秒（“击晕”生效的时间内，无法攻击和移动）</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Skill_06</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>SkillEffect_06_3</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2804,50 +2819,50 @@
       <c r="B32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>士兵普攻命中敌人</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>震晕</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”4秒（“击晕”生效的时间内，无法攻击和移动）</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Skill_06</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>SkillEffect_06_4</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2860,50 +2875,50 @@
       <c r="B33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>士兵普攻命中敌人</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>震晕</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>有10%的概率对目标敌人以及半径1.5范围内的所有敌人产生“击晕”5秒（“击晕”生效的时间内，无法攻击和移动）</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Skill_06</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>SkillEffect_06_5</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2916,45 +2931,45 @@
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>冰冻</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续2秒</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Skill_07</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>SkillEffect_07_1</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>10</v>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2967,45 +2982,45 @@
       <c r="B35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>冰冻</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续3秒</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Skill_07</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>SkillEffect_07_2</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>10</v>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3018,45 +3033,45 @@
       <c r="B36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>冰冻</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续4秒</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Skill_07</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>SkillEffect_07_3</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3069,45 +3084,45 @@
       <c r="B37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>冰冻</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续5秒</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>Skill_07</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>SkillEffect_07_4</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>10</v>
       </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3120,45 +3135,45 @@
       <c r="B38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>冰冻</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>普攻命中的敌人后，此敌人半径1.5范围内的所有敌人攻击和移动速度降低50%，持续6秒</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Skill_07</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>SkillEffect_07_5</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>10</v>
       </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3171,50 +3186,50 @@
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>目标敌人的MonsterType是精英(Elite)</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>精英克制</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>攻击的伤害增加50%</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Skill_08</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>SkillEffect_08_1</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3227,50 +3242,50 @@
       <c r="B40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>目标敌人的MonsterType是精英(Elite)</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>精英克制</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>攻击的伤害增加60%</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>Skill_08</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>SkillEffect_08_2</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3283,50 +3298,50 @@
       <c r="B41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>目标敌人的MonsterType是精英(Elite)</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>精英克制</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>攻击的伤害增加70%</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Skill_08</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>SkillEffect_08_3</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3339,50 +3354,50 @@
       <c r="B42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>目标敌人的MonsterType是精英(Elite)</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>精英克制</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>攻击的伤害增加80%</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Skill_08</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>SkillEffect_08_4</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3395,50 +3410,50 @@
       <c r="B43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>目标敌人的MonsterType是精英(Elite)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>精英克制</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>攻击的伤害增加90%</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>Skill_08</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>SkillEffect_08_5</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3451,45 +3466,45 @@
       <c r="B44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>渐入佳境</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>攻击增加3%，可以叠加效果，最大叠加到60%</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Skill_09</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>SkillEffect_09_1</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>10</v>
       </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3502,45 +3517,45 @@
       <c r="B45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>渐入佳境</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>攻击增加5%，可以叠加效果，最大叠加到60%</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>Skill_09</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>SkillEffect_09_2</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>10</v>
       </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3553,45 +3568,45 @@
       <c r="B46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>渐入佳境</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>攻击增加7%，可以叠加效果，最大叠加到60%</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>Skill_09</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>SkillEffect_09_3</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>10</v>
       </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3604,45 +3619,45 @@
       <c r="B47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>渐入佳境</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>攻击增加9%，可以叠加效果，最大叠加到60%</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>Skill_09</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>SkillEffect_09_4</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>10</v>
       </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3655,45 +3670,45 @@
       <c r="B48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>渐入佳境</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>攻击增加12%，可以叠加效果，最大叠加到60%</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Skill_09</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>SkillEffect_09_5</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>10</v>
       </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3706,45 +3721,45 @@
       <c r="B49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>贯穿</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下1名敌人，造成100%的伤害</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>SkillEffect_10_1</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3757,45 +3772,45 @@
       <c r="B50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>贯穿</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下2名敌人，造成100%的伤害</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>SkillEffect_10_2</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3808,45 +3823,45 @@
       <c r="B51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>贯穿</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下3名敌人，造成100%的伤害</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>SkillEffect_10_3</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3859,45 +3874,45 @@
       <c r="B52" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>贯穿</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下4名敌人，造成100%的伤害</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>SkillEffect_10_4</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3910,45 +3925,45 @@
       <c r="B53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>贯穿</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>发射的箭矢命中1名敌人后，子弹不会消失，可以继续飞行，命中下5名敌人，造成100%的伤害</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>SkillEffect_10_5</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3961,45 +3976,45 @@
       <c r="B54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>灼烧</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续2秒，再次施加“灼烧”则叠加灼烧的时间）</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>Skill_11</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>SkillEffect_11_1</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4012,45 +4027,45 @@
       <c r="B55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>灼烧</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续3秒，再次施加“灼烧”则叠加灼烧的时间）</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>Skill_11</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>SkillEffect_11_2</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>0</v>
       </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4063,45 +4078,45 @@
       <c r="B56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>灼烧</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续4秒，再次施加“灼烧”则叠加灼烧的时间）</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>Skill_11</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>SkillEffect_11_3</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4114,45 +4129,45 @@
       <c r="B57" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>灼烧</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续5秒，再次施加“灼烧”则叠加灼烧的时间）</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>Skill_11</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>SkillEffect_11_4</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4165,45 +4180,45 @@
       <c r="B58" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>灼烧</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>普攻命中的敌人施加“灼烧“效果（每1秒造成自身普攻20%伤害的伤害，持续6秒，再次施加“灼烧”则叠加灼烧的时间）</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>Skill_11</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>SkillEffect_11_5</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>0</v>
       </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4216,50 +4231,50 @@
       <c r="B59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>当开始寻找新的攻击目标</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>瞬移</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>更换选择的目标为“距离自己最远的敌人”，目标确定后“瞬移”到该敌人的背后</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>Skill_12</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>SkillEffect_12_1</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>60</v>
       </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4272,50 +4287,50 @@
       <c r="B60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>当开始寻找新的攻击目标</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>瞬移</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>更换选择的目标为“距离自己最远的敌人”，目标确定后“瞬移”到该敌人的背后</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Skill_12</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>SkillEffect_12_2</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>50</v>
       </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4328,50 +4343,50 @@
       <c r="B61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>当开始寻找新的攻击目标</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>瞬移</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>更换选择的目标为“距离自己最远的敌人”，目标确定后“瞬移”到该敌人的背后</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Skill_12</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>SkillEffect_12_3</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>40</v>
       </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4384,50 +4399,50 @@
       <c r="B62" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>当开始寻找新的攻击目标</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>瞬移</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>更换选择的目标为“距离自己最远的敌人”，目标确定后“瞬移”到该敌人的背后</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>Skill_12</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>SkillEffect_12_4</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>30</v>
       </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4440,51 +4455,151 @@
       <c r="B63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Mode2</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>当开始寻找新的攻击目标</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>瞬移</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>更换选择的目标为“距离自己最远的敌人”，目标确定后“瞬移”到该敌人的背后</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>Skill_12</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>SkillEffect_12_5</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>20</v>
       </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Form_Wedge_01</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>楔阵</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>战术阵型标记技能；制造授予后用于组阵判定，不驱动战斗</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>平行阵</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>战术阵型标记技能；制造授予后用于组阵判定，不驱动战斗</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
